--- a/1.7. EXCEL  SECTION - Advanced Formulas and Functions/1.7.2.1 Advanced Formulas - VLookup working file.xlsx
+++ b/1.7. EXCEL  SECTION - Advanced Formulas and Functions/1.7.2.1 Advanced Formulas - VLookup working file.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="28702"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/travis/Desktop/Database Lookup and Functions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rittiv/Documents/GitHub/Projects-Data/1.7. EXCEL  SECTION - Advanced Formulas and Functions/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3AE5D8-E06E-974B-8A4E-F47603C6286F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="6120" windowWidth="25600" windowHeight="14400"/>
+    <workbookView xWindow="25600" yWindow="620" windowWidth="25600" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="marketing_perf" sheetId="6" r:id="rId1"/>
@@ -17,10 +18,21 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">marketing_perf!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="150001" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -1238,11 +1250,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="44" formatCode="_(&quot;HK$&quot;* #,##0.00_);_(&quot;HK$&quot;* \(#,##0.00\);_(&quot;HK$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="[$-409]mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;HK$&quot;* #,##0.00_);_(&quot;HK$&quot;* \(#,##0.00\);_(&quot;HK$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]mmm\-yy;@"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -1789,7 +1801,7 @@
     <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1798,28 +1810,28 @@
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="19" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="19" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="19" fillId="33" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="19" fillId="33" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="21" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="19" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="21" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="19" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="21" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="47">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1875,6 +1887,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2166,7 +2181,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M381"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2251,9 +2266,18 @@
       <c r="J2" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K2" s="14"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="17"/>
+      <c r="K2" s="14" t="str">
+        <f>VLOOKUP(J2, A1:H381, 2, FALSE)</f>
+        <v>Designer</v>
+      </c>
+      <c r="L2" s="15">
+        <f>VLOOKUP(J2, $A$1:$H$381, 7, FALSE)</f>
+        <v>250</v>
+      </c>
+      <c r="M2" s="17">
+        <f>VLOOKUP(J2,A1:H381, 8, FALSE)</f>
+        <v>13.11</v>
+      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
@@ -2283,9 +2307,18 @@
       <c r="J3" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="17"/>
+      <c r="K3" s="14" t="str">
+        <f t="shared" ref="K3:K11" si="0">VLOOKUP(J3, A2:H382, 2, FALSE)</f>
+        <v>None</v>
+      </c>
+      <c r="L3" s="15">
+        <f t="shared" ref="L3:L11" si="1">VLOOKUP(J3, $A$1:$H$381, 7, FALSE)</f>
+        <v>260</v>
+      </c>
+      <c r="M3" s="17">
+        <f t="shared" ref="M3:M11" si="2">VLOOKUP(J3,A2:H382, 8, FALSE)</f>
+        <v>22.6</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
@@ -2315,9 +2348,18 @@
       <c r="J4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="14"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="17"/>
+      <c r="K4" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Discount</v>
+      </c>
+      <c r="L4" s="15">
+        <f t="shared" si="1"/>
+        <v>966</v>
+      </c>
+      <c r="M4" s="17">
+        <f t="shared" si="2"/>
+        <v>465.24</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
@@ -2347,9 +2389,18 @@
       <c r="J5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="17"/>
+      <c r="K5" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="L5" s="15">
+        <f t="shared" si="1"/>
+        <v>720</v>
+      </c>
+      <c r="M5" s="17">
+        <f t="shared" si="2"/>
+        <v>11.92</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
@@ -2379,9 +2430,18 @@
       <c r="J6" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="17"/>
+      <c r="K6" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Discount</v>
+      </c>
+      <c r="L6" s="15">
+        <f t="shared" si="1"/>
+        <v>632</v>
+      </c>
+      <c r="M6" s="17">
+        <f t="shared" si="2"/>
+        <v>159.16</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
@@ -2411,9 +2471,18 @@
       <c r="J7" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="17"/>
+      <c r="K7" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="L7" s="15">
+        <f t="shared" si="1"/>
+        <v>160.6</v>
+      </c>
+      <c r="M7" s="17">
+        <f t="shared" si="2"/>
+        <v>111.2</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
@@ -2443,9 +2512,18 @@
       <c r="J8" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="K8" s="14"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="17"/>
+      <c r="K8" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Designer</v>
+      </c>
+      <c r="L8" s="15">
+        <f t="shared" si="1"/>
+        <v>413</v>
+      </c>
+      <c r="M8" s="17">
+        <f t="shared" si="2"/>
+        <v>67</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
@@ -2475,9 +2553,18 @@
       <c r="J9" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="17"/>
+      <c r="K9" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Designer</v>
+      </c>
+      <c r="L9" s="15">
+        <f t="shared" si="1"/>
+        <v>258</v>
+      </c>
+      <c r="M9" s="17">
+        <f t="shared" si="2"/>
+        <v>135.78</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
@@ -2507,9 +2594,18 @@
       <c r="J10" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="K10" s="14"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="17"/>
+      <c r="K10" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="L10" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="17">
+        <f t="shared" si="2"/>
+        <v>5.0199999999999996</v>
+      </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
@@ -2539,9 +2635,18 @@
       <c r="J11" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="K11" s="14"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="17"/>
+      <c r="K11" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="L11" s="15">
+        <f t="shared" si="1"/>
+        <v>467.83</v>
+      </c>
+      <c r="M11" s="17">
+        <f t="shared" si="2"/>
+        <v>295.19</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
@@ -12164,9 +12269,10 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:H383">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H383">
     <sortCondition descending="1" ref="G2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>